--- a/data/trans_orig/P33_2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P33_2_2023-Estudios-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de horas que duerme habitualmente al día durante los fines de semana</t>
+          <t>Número medio de horas que duerme habitualmente al día durante los fines de semana (tasa de respuesta: 97,11%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,12 +571,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,11; 7,33</t>
+          <t>7,12; 7,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,96; 7,11</t>
+          <t>6,96; 7,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,42; 8,63</t>
+          <t>7,43; 8,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,85; 7,3</t>
+          <t>6,83; 7,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,25; 7,9</t>
+          <t>7,24; 7,9</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,21; 7,42</t>
+          <t>7,21; 7,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,27; 7,4</t>
+          <t>7,26; 7,39</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,36; 8,06</t>
+          <t>7,36; 8,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,96; 7,26</t>
+          <t>6,97; 7,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,23; 7,7</t>
+          <t>7,24; 7,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33_2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P33_2_2023-Estudios-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>7,23</t>
+          <t>7,25</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7,04</t>
+          <t>7,03</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,11</t>
+          <t>7,12</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,12; 7,33</t>
+          <t>7,14; 7,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,96; 7,12</t>
+          <t>6,95; 7,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,05; 7,18</t>
+          <t>7,06; 7,18</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,73</t>
+          <t>7,43</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,17</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,45</t>
+          <t>7,38</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,43; 8,44</t>
+          <t>7,37; 7,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 7,31</t>
+          <t>7,26; 7,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,24; 7,9</t>
+          <t>7,34; 7,42</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7,31</t>
+          <t>7,34</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7,35</t>
+          <t>7,34</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,33</t>
+          <t>7,34</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,21; 7,41</t>
+          <t>7,23; 7,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,26; 7,43</t>
+          <t>7,26; 7,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,26; 7,39</t>
+          <t>7,28; 7,4</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7,57</t>
+          <t>7,38</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7,17</t>
+          <t>7,26</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,37</t>
+          <t>7,32</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,36; 8,13</t>
+          <t>7,34; 7,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,97; 7,26</t>
+          <t>7,22; 7,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,24; 7,69</t>
+          <t>7,29; 7,35</t>
         </is>
       </c>
     </row>
